--- a/data/trans_dic/P16A09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,65</t>
+          <t>0,15; 1,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,78</t>
+          <t>0,04; 1,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,91</t>
+          <t>0,07; 0,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,94</t>
+          <t>0,08; 0,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,2</t>
+          <t>0,13; 1,24</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,29</t>
+          <t>0,44; 2,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,87</t>
+          <t>0,39; 1,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,44</t>
+          <t>0,15; 1,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,29</t>
+          <t>0,68; 2,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,19</t>
+          <t>0,23; 1,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,06</t>
+          <t>0,28; 1,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,95</t>
+          <t>0,21; 0,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,52</t>
+          <t>0,5; 1,54</t>
         </is>
       </c>
     </row>
@@ -1137,47 +1137,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,62</t>
+          <t>0,9; 3,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,48</t>
+          <t>0,34; 2,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,47</t>
+          <t>0,17; 1,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,65</t>
+          <t>0,49; 2,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,8</t>
+          <t>1,51; 4,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,2</t>
+          <t>1,57; 4,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,45</t>
+          <t>1,46; 4,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,85</t>
+          <t>2,01; 5,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,34</t>
+          <t>1,47; 3,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,6</t>
+          <t>1,02; 2,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,51</t>
+          <t>1,26; 3,56</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,66</t>
+          <t>5,2; 10,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,88</t>
+          <t>1,46; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,24</t>
+          <t>0,98; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,86</t>
+          <t>1,4; 3,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,04</t>
+          <t>6,24; 12,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 12,14</t>
+          <t>6,56; 12,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,36</t>
+          <t>3,76; 7,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,75</t>
+          <t>5,34; 8,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 10,26</t>
+          <t>6,56; 10,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,66</t>
+          <t>4,49; 7,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,42</t>
+          <t>2,69; 5,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,81</t>
+          <t>3,66; 5,68</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 9,1</t>
+          <t>3,69; 9,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,07</t>
+          <t>2,68; 7,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,1</t>
+          <t>1,45; 5,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,79</t>
+          <t>2,0; 4,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,06; 19,71</t>
+          <t>12,1; 19,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,2; 19,42</t>
+          <t>11,83; 19,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,5</t>
+          <t>6,61; 12,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 13,58</t>
+          <t>3,43; 13,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,77</t>
+          <t>9,02; 13,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,09; 13,03</t>
+          <t>8,22; 13,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,22</t>
+          <t>4,67; 8,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,63</t>
+          <t>3,54; 8,57</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,16; 23,74</t>
+          <t>13,66; 23,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,69; 19,15</t>
+          <t>9,4; 18,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,54</t>
+          <t>5,17; 11,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,53</t>
+          <t>4,58; 9,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,06; 21,65</t>
+          <t>12,98; 22,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,37; 27,02</t>
+          <t>17,86; 26,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 15,43</t>
+          <t>8,7; 15,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,9; 16,52</t>
+          <t>11,75; 16,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,44; 21,02</t>
+          <t>14,48; 21,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,87; 22,12</t>
+          <t>16,02; 22,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 13,26</t>
+          <t>7,8; 12,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,19; 12,8</t>
+          <t>9,57; 12,97</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,54</t>
+          <t>2,39; 3,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,67</t>
+          <t>1,6; 2,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,79</t>
+          <t>0,98; 1,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,29</t>
+          <t>1,31; 2,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,9</t>
+          <t>4,33; 5,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,63</t>
+          <t>5,0; 6,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,46</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,88</t>
+          <t>4,2; 5,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,48</t>
+          <t>3,55; 4,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,53</t>
+          <t>3,54; 4,5</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,01</t>
+          <t>2,2; 3,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,92</t>
+          <t>2,99; 3,98</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1950</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6876</t>
+          <t>0; 8602</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 14616</t>
+          <t>0; 14050</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1867</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7713</t>
+          <t>0; 6738</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 16150</t>
+          <t>0; 14872</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4165</t>
+          <t>0; 4788</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>997; 11351</t>
+          <t>999; 10615</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1996</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6409</t>
+          <t>0; 5351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 11384</t>
+          <t>0; 10116</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2049</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6884</t>
+          <t>0; 7887</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>145; 9099</t>
+          <t>185; 8887</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>952; 12373</t>
+          <t>945; 10938</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>999; 12150</t>
+          <t>1001; 11529</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6908</t>
+          <t>0; 5948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1213; 11261</t>
+          <t>1201; 11626</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6092</t>
+          <t>0; 4875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7153</t>
+          <t>0; 7187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7614</t>
+          <t>0; 8733</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3054; 15800</t>
+          <t>3033; 15420</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2930; 13235</t>
+          <t>2766; 12742</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>971; 9530</t>
+          <t>968; 9222</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3689; 12388</t>
+          <t>3661; 12477</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3100; 15736</t>
+          <t>3058; 15316</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3109; 14673</t>
+          <t>3890; 15225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2000; 12628</t>
+          <t>2779; 12637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4931; 16364</t>
+          <t>5383; 16639</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4620; 18791</t>
+          <t>4658; 17775</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2064; 15270</t>
+          <t>2096; 15368</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1078; 9515</t>
+          <t>1081; 8745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4384; 23560</t>
+          <t>4306; 23146</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7308; 24747</t>
+          <t>7808; 23213</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8788; 25784</t>
+          <t>9623; 26479</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10392; 28887</t>
+          <t>9477; 28599</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14398; 41732</t>
+          <t>14361; 41227</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14560; 34612</t>
+          <t>15244; 36040</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13993; 34627</t>
+          <t>14034; 34664</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12940; 33728</t>
+          <t>13160; 32447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20404; 56258</t>
+          <t>20236; 56998</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19743; 41215</t>
+          <t>20102; 41612</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6143; 20911</t>
+          <t>6272; 20733</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5078; 20240</t>
+          <t>4672; 19826</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7481; 21627</t>
+          <t>7832; 21496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25557; 48635</t>
+          <t>25202; 49031</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29542; 54347</t>
+          <t>29372; 54703</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18531; 41532</t>
+          <t>18698; 39173</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29230; 47700</t>
+          <t>29096; 46706</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49691; 81143</t>
+          <t>51866; 84138</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38236; 67102</t>
+          <t>39375; 67857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27323; 52846</t>
+          <t>26265; 53314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41298; 64212</t>
+          <t>40470; 62764</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11120; 26639</t>
+          <t>10794; 27548</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8130; 24828</t>
+          <t>8249; 24151</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5091; 17064</t>
+          <t>4858; 17442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7039; 17602</t>
+          <t>7366; 17847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41342; 67609</t>
+          <t>41489; 67545</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39531; 68554</t>
+          <t>41756; 69001</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24866; 47219</t>
+          <t>24956; 47564</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19670; 82608</t>
+          <t>20861; 82975</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56842; 87493</t>
+          <t>57340; 87099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53495; 86107</t>
+          <t>54322; 88821</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33568; 58564</t>
+          <t>33249; 59159</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30666; 84231</t>
+          <t>34527; 83597</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>27622; 49829</t>
+          <t>28672; 50076</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24119; 47687</t>
+          <t>23401; 46962</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13123; 29660</t>
+          <t>13297; 28684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13524; 26892</t>
+          <t>12919; 26113</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43618; 72304</t>
+          <t>43356; 74379</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70854; 104208</t>
+          <t>68902; 103780</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34973; 61739</t>
+          <t>34828; 62663</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>50482; 70119</t>
+          <t>49867; 70653</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78497; 114310</t>
+          <t>78730; 115415</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100722; 140376</t>
+          <t>101677; 139952</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53912; 87161</t>
+          <t>51249; 83174</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>64926; 90467</t>
+          <t>67653; 91680</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>77076; 115878</t>
+          <t>78300; 114764</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>55242; 91401</t>
+          <t>54702; 90999</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34225; 60827</t>
+          <t>33114; 59638</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45805; 79269</t>
+          <t>45136; 78273</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>147850; 199364</t>
+          <t>146473; 198455</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>181182; 235216</t>
+          <t>177098; 236451</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>110223; 158235</t>
+          <t>111719; 159042</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>152825; 215091</t>
+          <t>153628; 214832</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>235279; 298426</t>
+          <t>236178; 301417</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>245081; 315223</t>
+          <t>246216; 313136</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154896; 209063</t>
+          <t>152690; 209726</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>211225; 278841</t>
+          <t>212623; 282968</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
     </row>
@@ -804,39 +804,39 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,55</t>
+          <t>0,15; 1,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,74</t>
+          <t>0,21; 2,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,8</t>
+          <t>0,07; 0,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,89</t>
+          <t>0,08; 0,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,24</t>
+          <t>0,13; 1,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,24</t>
+          <t>0,44; 2,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,81</t>
+          <t>0,43; 2,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,39</t>
+          <t>0,15; 1,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,3</t>
+          <t>0,65; 2,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,15</t>
+          <t>0,22; 1,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,1</t>
+          <t>0,28; 1,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,95</t>
+          <t>0,21; 0,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,54</t>
+          <t>0,5; 1,43</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,42</t>
+          <t>0,93; 3,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,5</t>
+          <t>0,34; 2,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,35</t>
+          <t>0,17; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,61</t>
+          <t>1,06; 3,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,5</t>
+          <t>1,42; 4,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,31</t>
+          <t>1,6; 4,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,41</t>
+          <t>1,68; 4,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,78</t>
+          <t>1,85; 3,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,48</t>
+          <t>1,45; 3,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,82</t>
+          <t>1,15; 2,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,51</t>
+          <t>1,03; 2,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,56</t>
+          <t>1,71; 3,25</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,76</t>
+          <t>5,18; 10,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,84</t>
+          <t>1,36; 4,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,15</t>
+          <t>1,03; 4,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,84</t>
+          <t>1,45; 4,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,24; 12,14</t>
+          <t>6,33; 12,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 12,22</t>
+          <t>6,51; 12,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,88</t>
+          <t>3,56; 8,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,57</t>
+          <t>5,52; 8,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,64</t>
+          <t>6,38; 10,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,74</t>
+          <t>4,49; 7,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,47</t>
+          <t>2,78; 5,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,68</t>
+          <t>3,65; 5,65</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,42</t>
+          <t>3,55; 8,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,85</t>
+          <t>2,63; 7,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,22</t>
+          <t>1,48; 5,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,86</t>
+          <t>1,89; 4,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,1; 19,7</t>
+          <t>11,88; 19,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,83; 19,54</t>
+          <t>11,82; 19,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,59</t>
+          <t>6,54; 12,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,43; 13,64</t>
+          <t>10,9; 15,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,02; 13,71</t>
+          <t>8,9; 13,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,44</t>
+          <t>8,07; 13,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,31</t>
+          <t>4,65; 8,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,57</t>
+          <t>7,07; 9,85</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,66; 23,86</t>
+          <t>13,32; 23,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 18,86</t>
+          <t>9,51; 19,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,16</t>
+          <t>5,05; 10,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,25</t>
+          <t>4,49; 9,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,98; 22,28</t>
+          <t>12,98; 22,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,86; 26,91</t>
+          <t>18,0; 27,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 15,66</t>
+          <t>8,71; 15,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,65</t>
+          <t>11,72; 16,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,48; 21,22</t>
+          <t>14,27; 20,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,02; 22,05</t>
+          <t>15,86; 22,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,66</t>
+          <t>8,03; 13,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,57; 12,97</t>
+          <t>9,52; 13,04</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,5</t>
+          <t>2,4; 3,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,66</t>
+          <t>1,65; 2,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,76</t>
+          <t>0,97; 1,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,26</t>
+          <t>1,49; 2,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,87</t>
+          <t>4,35; 5,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,67</t>
+          <t>5,04; 6,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,49</t>
+          <t>3,11; 4,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,87</t>
+          <t>4,89; 6,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,53</t>
+          <t>3,54; 4,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,5</t>
+          <t>3,55; 4,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,02</t>
+          <t>2,23; 2,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,98</t>
+          <t>3,35; 4,08</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>5113</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 8602</t>
+          <t>0; 7800</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 14050</t>
+          <t>0; 17698</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6738</t>
+          <t>0; 6743</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 14872</t>
+          <t>0; 18824</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4805</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4788</t>
+          <t>0; 5399</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>999; 10615</t>
+          <t>998; 11542</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5351</t>
+          <t>0; 7436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 10116</t>
+          <t>0; 10715</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2306,32 +2306,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7887</t>
+          <t>0; 6260</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>185; 8887</t>
+          <t>1077; 10403</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>945; 10938</t>
+          <t>950; 11560</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1001; 11529</t>
+          <t>999; 12390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5948</t>
+          <t>0; 6881</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1201; 11626</t>
+          <t>1241; 10839</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>10822</t>
         </is>
       </c>
     </row>
@@ -2489,57 +2489,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4875</t>
+          <t>0; 4857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7187</t>
+          <t>0; 7279</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 8733</t>
+          <t>0; 7576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3033; 15420</t>
+          <t>3025; 15162</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2766; 12742</t>
+          <t>3027; 14622</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>968; 9222</t>
+          <t>980; 9380</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3661; 12477</t>
+          <t>4046; 14277</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3058; 15316</t>
+          <t>2968; 15223</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3890; 15225</t>
+          <t>3867; 14839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2779; 12637</t>
+          <t>2774; 12105</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5383; 16639</t>
+          <t>6245; 17759</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36022</t>
+          <t>33782</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4658; 17775</t>
+          <t>4843; 17705</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2096; 15368</t>
+          <t>2081; 14822</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1081; 8745</t>
+          <t>1077; 8772</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4306; 23146</t>
+          <t>7421; 23312</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7808; 23213</t>
+          <t>7319; 22165</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9623; 26479</t>
+          <t>9805; 25938</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9477; 28599</t>
+          <t>10933; 29468</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14361; 41227</t>
+          <t>13606; 28488</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15244; 36040</t>
+          <t>15034; 35607</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14034; 34664</t>
+          <t>14152; 35108</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13160; 32447</t>
+          <t>13373; 32902</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20236; 56998</t>
+          <t>24618; 46691</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37533</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51006</t>
+          <t>56405</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20102; 41612</t>
+          <t>20033; 41661</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6272; 20733</t>
+          <t>5807; 21139</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4672; 19826</t>
+          <t>4899; 21346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7832; 21496</t>
+          <t>8821; 24857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25202; 49031</t>
+          <t>25584; 48644</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29372; 54703</t>
+          <t>29164; 54759</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18698; 39173</t>
+          <t>17694; 39892</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29096; 46706</t>
+          <t>33518; 52236</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51866; 84138</t>
+          <t>50423; 83300</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39375; 67857</t>
+          <t>39372; 69439</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26265; 53314</t>
+          <t>27105; 51900</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>40470; 62764</t>
+          <t>44411; 68699</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>51818</t>
+          <t>58199</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63414</t>
+          <t>71034</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10794; 27548</t>
+          <t>10381; 26155</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8249; 24151</t>
+          <t>8090; 23699</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4858; 17442</t>
+          <t>4941; 17135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7366; 17847</t>
+          <t>7692; 19242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41489; 67545</t>
+          <t>40739; 65934</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41756; 69001</t>
+          <t>41744; 69259</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24956; 47564</t>
+          <t>24709; 48358</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20861; 82975</t>
+          <t>47881; 69187</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>57340; 87099</t>
+          <t>56541; 86836</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54322; 88821</t>
+          <t>53316; 85990</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33249; 59159</t>
+          <t>33091; 58955</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34527; 83597</t>
+          <t>59788; 83243</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>59674</t>
+          <t>66466</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78736</t>
+          <t>87575</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>28672; 50076</t>
+          <t>27955; 48541</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23401; 46962</t>
+          <t>23678; 48061</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13297; 28684</t>
+          <t>12973; 27911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12919; 26113</t>
+          <t>13910; 29277</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43356; 74379</t>
+          <t>43333; 74523</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>68902; 103780</t>
+          <t>69447; 104705</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34828; 62663</t>
+          <t>34861; 61802</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>49867; 70653</t>
+          <t>54251; 77667</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>78730; 115415</t>
+          <t>77608; 112501</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101677; 139952</t>
+          <t>100680; 140331</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51249; 83174</t>
+          <t>52763; 86990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>67653; 91680</t>
+          <t>73603; 100801</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>203735</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>246942</t>
+          <t>269535</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>78300; 114764</t>
+          <t>78523; 115374</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>54702; 90999</t>
+          <t>56285; 91026</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33114; 59638</t>
+          <t>33086; 60175</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45136; 78273</t>
+          <t>52578; 83495</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>146473; 198455</t>
+          <t>147081; 200905</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>177098; 236451</t>
+          <t>178549; 236700</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>111719; 159042</t>
+          <t>110235; 158867</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>153628; 214832</t>
+          <t>182405; 226977</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>236178; 301417</t>
+          <t>235431; 299774</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>246216; 313136</t>
+          <t>247370; 309906</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>152690; 209726</t>
+          <t>154872; 206987</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>212623; 282968</t>
+          <t>242954; 296333</t>
         </is>
       </c>
     </row>
